--- a/data/trans_dic/PCS12_SP_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R2-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>35,93; 45,25</t>
+          <t>36,3; 45,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,07; 40,99</t>
+          <t>31,29; 41,14</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,31; 39,33</t>
+          <t>30,2; 39,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41,32; 50,54</t>
+          <t>41,12; 50,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,93; 54,78</t>
+          <t>42,82; 53,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,14; 48,53</t>
+          <t>37,04; 48,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,13; 38,56</t>
+          <t>28,16; 38,29</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,38; 47,1</t>
+          <t>39,41; 47,15</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,54; 47,05</t>
+          <t>40,15; 47,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,5; 42,87</t>
+          <t>35,46; 42,65</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,58; 37,71</t>
+          <t>30,5; 37,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,68; 47,52</t>
+          <t>41,62; 47,59</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,32; 44,82</t>
+          <t>34,65; 45,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,22; 49,35</t>
+          <t>39,43; 50,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,14; 38,07</t>
+          <t>28,1; 38,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38,18; 48,03</t>
+          <t>38,57; 48,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,09; 45,61</t>
+          <t>35,73; 46,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,26; 46,73</t>
+          <t>35,33; 46,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,4; 42,62</t>
+          <t>32,41; 42,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,88; 49,41</t>
+          <t>40,85; 49,46</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,43; 43,76</t>
+          <t>36,51; 43,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39,2; 46,74</t>
+          <t>39,08; 46,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,51; 38,77</t>
+          <t>31,28; 38,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,55; 46,88</t>
+          <t>40,98; 47,44</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,69; 48,2</t>
+          <t>39,51; 47,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45,46; 53,77</t>
+          <t>46,02; 54,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,44; 47,92</t>
+          <t>39,3; 48,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47,35; 88,53</t>
+          <t>47,11; 87,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>47,73; 63,46</t>
+          <t>48,07; 64,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,76; 62,04</t>
+          <t>49,41; 61,85</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,82; 55,49</t>
+          <t>40,34; 55,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,7; 64,48</t>
+          <t>52,13; 64,08</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43,03; 50,57</t>
+          <t>42,99; 50,38</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48,32; 55,09</t>
+          <t>48,07; 54,92</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40,85; 48,59</t>
+          <t>40,8; 48,29</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50,42; 85,49</t>
+          <t>50,41; 84,92</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,16; 50,8</t>
+          <t>45,25; 50,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,42; 50,23</t>
+          <t>44,08; 50,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,57; 46,51</t>
+          <t>40,37; 46,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>44,74; 51,69</t>
+          <t>45,01; 51,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,51; 57,91</t>
+          <t>50,35; 57,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,41; 51,42</t>
+          <t>44,25; 51,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,92; 47,73</t>
+          <t>40,74; 47,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,84; 80,32</t>
+          <t>51,43; 80,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,92; 52,3</t>
+          <t>47,99; 52,54</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,17; 50,01</t>
+          <t>45,25; 50,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41,57; 45,8</t>
+          <t>41,42; 45,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,2; 68,52</t>
+          <t>49,35; 70,62</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>44,08; 54,61</t>
+          <t>44,1; 55,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,06; 51,34</t>
+          <t>42,67; 51,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37,8; 45,78</t>
+          <t>38,06; 46,17</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,24; 58,52</t>
+          <t>48,34; 58,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,15; 62,46</t>
+          <t>54,67; 62,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,63; 66,12</t>
+          <t>58,76; 65,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,27; 58,77</t>
+          <t>51,4; 58,82</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>39,52; 61,67</t>
+          <t>41,64; 62,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,51; 58,29</t>
+          <t>51,59; 58,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53,4; 58,95</t>
+          <t>53,07; 58,86</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46,12; 51,8</t>
+          <t>46,36; 51,83</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>45,38; 59,23</t>
+          <t>43,71; 58,99</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,58; 22,63</t>
+          <t>13,69; 22,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,85; 29,3</t>
+          <t>18,72; 29,52</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,63; 26,02</t>
+          <t>16,59; 26,52</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,83; 31,3</t>
+          <t>13,69; 30,53</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>62,67; 67,98</t>
+          <t>62,44; 67,67</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56,82; 63,06</t>
+          <t>56,82; 62,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,42; 56,77</t>
+          <t>50,73; 57,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53,19; 60,11</t>
+          <t>53,05; 60,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53,56; 58,25</t>
+          <t>53,64; 58,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50,33; 55,86</t>
+          <t>50,54; 55,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44,18; 49,66</t>
+          <t>44,2; 49,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44,38; 51,97</t>
+          <t>44,56; 51,7</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,96; 44,31</t>
+          <t>40,77; 44,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42,4; 45,76</t>
+          <t>42,3; 45,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37,36; 40,77</t>
+          <t>37,36; 40,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45,34; 62,45</t>
+          <t>45,29; 62,36</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>55,35; 58,72</t>
+          <t>55,28; 58,7</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,52; 55,94</t>
+          <t>52,39; 55,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,94; 49,38</t>
+          <t>46,01; 49,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>50,96; 64,09</t>
+          <t>51,03; 63,37</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,66; 51,1</t>
+          <t>48,69; 51,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47,98; 50,4</t>
+          <t>47,95; 50,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42,44; 44,73</t>
+          <t>42,28; 44,68</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>48,96; 57,95</t>
+          <t>49,23; 59,16</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>170209; 214363</t>
+          <t>171982; 214669</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>135850; 179220</t>
+          <t>136804; 179861</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>130064; 168757</t>
+          <t>129566; 168502</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>207865; 254230</t>
+          <t>206855; 253541</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>131657; 167986</t>
+          <t>131320; 165400</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>116796; 152611</t>
+          <t>116468; 153109</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97630; 133829</t>
+          <t>97716; 132875</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>175704; 210166</t>
+          <t>175836; 210377</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>308590; 367237</t>
+          <t>313385; 367317</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>266871; 322208</t>
+          <t>266538; 320558</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>237351; 292699</t>
+          <t>236710; 291077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>395680; 451097</t>
+          <t>395063; 451719</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>125924; 164462</t>
+          <t>127160; 165312</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>164244; 206664</t>
+          <t>165124; 211740</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>106164; 143617</t>
+          <t>105999; 143478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172376; 216850</t>
+          <t>174119; 216709</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>134202; 169625</t>
+          <t>132870; 172977</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>119186; 157936</t>
+          <t>119435; 157867</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>120619; 158653</t>
+          <t>120656; 159780</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>156159; 188768</t>
+          <t>156032; 188957</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>269148; 323278</t>
+          <t>269715; 321556</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>296632; 353755</t>
+          <t>295729; 355579</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>236195; 290579</t>
+          <t>234474; 288248</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>337956; 390754</t>
+          <t>341536; 395373</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>215290; 261443</t>
+          <t>214276; 258246</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>286132; 338417</t>
+          <t>289643; 342099</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>205817; 250113</t>
+          <t>205117; 251260</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>315024; 589071</t>
+          <t>313458; 582420</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80075; 106478</t>
+          <t>80659; 107577</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>129451; 161380</t>
+          <t>128524; 160877</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>64496; 92175</t>
+          <t>67020; 92979</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>85776; 106979</t>
+          <t>86492; 106330</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>305619; 359103</t>
+          <t>305282; 357787</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>429811; 490011</t>
+          <t>427605; 488505</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>281030; 334317</t>
+          <t>280689; 332277</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>419156; 710633</t>
+          <t>419056; 705891</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>559255; 629104</t>
+          <t>560304; 630059</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>514792; 582217</t>
+          <t>510854; 584660</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>466369; 534723</t>
+          <t>464139; 532680</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>460698; 532228</t>
+          <t>463519; 532415</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>360815; 413619</t>
+          <t>359646; 414093</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>340489; 394245</t>
+          <t>339233; 394345</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>337961; 394216</t>
+          <t>336495; 395549</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>496064; 783755</t>
+          <t>501873; 783371</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>935653; 1021173</t>
+          <t>937149; 1025809</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>869864; 962959</t>
+          <t>871347; 963809</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>821299; 904698</t>
+          <t>818216; 905166</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>986802; 1374217</t>
+          <t>989790; 1416338</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>154516; 191451</t>
+          <t>154591; 193034</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>214768; 262156</t>
+          <t>217860; 260603</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>234627; 284147</t>
+          <t>236258; 286575</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>226926; 275284</t>
+          <t>227433; 272873</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>307996; 355245</t>
+          <t>310945; 357316</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>446455; 503481</t>
+          <t>447438; 500570</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>378490; 433873</t>
+          <t>379425; 434241</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>330681; 515924</t>
+          <t>348371; 526828</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>473541; 535868</t>
+          <t>474256; 535028</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>679306; 749965</t>
+          <t>675073; 748814</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>626690; 703936</t>
+          <t>630032; 704354</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>593184; 774211</t>
+          <t>571351; 771029</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40505; 67487</t>
+          <t>40811; 67453</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>50296; 78200</t>
+          <t>49959; 78787</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47763; 74702</t>
+          <t>47628; 76151</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33261; 75273</t>
+          <t>32925; 73425</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>782610; 848892</t>
+          <t>779739; 845004</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>630307; 699577</t>
+          <t>630292; 696580</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>545533; 614289</t>
+          <t>548892; 617164</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>400290; 452388</t>
+          <t>399301; 453217</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>828506; 901141</t>
+          <t>829746; 905247</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>692635; 768737</t>
+          <t>695603; 765175</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>604920; 679991</t>
+          <t>605234; 680483</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>440718; 516104</t>
+          <t>442574; 513487</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1339546; 1448996</t>
+          <t>1333166; 1446918</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1450721; 1565787</t>
+          <t>1447413; 1566864</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1264994; 1380422</t>
+          <t>1264804; 1375769</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1523793; 2098511</t>
+          <t>1521905; 2095734</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1869654; 1983498</t>
+          <t>1867456; 1983039</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1864369; 1985926</t>
+          <t>1859988; 1984006</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1622413; 1743788</t>
+          <t>1624911; 1749141</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1813807; 2281169</t>
+          <t>1816313; 2255467</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3235053; 3397116</t>
+          <t>3236790; 3397505</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3345325; 3514254</t>
+          <t>3343100; 3518116</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2935637; 3093909</t>
+          <t>2924978; 3090987</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3387666; 4009899</t>
+          <t>3406847; 4093778</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/PCS12_SP_R2-Clase-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R2-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,6%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>36,3; 45,31</t>
+          <t>36,01; 44,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,29; 41,14</t>
+          <t>31,7; 41,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,2; 39,27</t>
+          <t>30,28; 39,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41,12; 50,4</t>
+          <t>41,62; 50,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,82; 53,93</t>
+          <t>42,52; 54,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,04; 48,69</t>
+          <t>36,5; 48,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,16; 38,29</t>
+          <t>28,54; 38,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>39,41; 47,15</t>
+          <t>39,81; 47,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>40,15; 47,06</t>
+          <t>40,12; 47,08</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>35,46; 42,65</t>
+          <t>35,15; 42,57</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,5; 37,5</t>
+          <t>30,82; 37,74</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>41,62; 47,59</t>
+          <t>41,76; 47,79</t>
         </is>
       </c>
     </row>
@@ -804,39 +804,39 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
+          <t>42,49%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>40,61%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>41,01%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>37,3%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>45,8%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>40,06%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>42,92%</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>40,61%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>41,01%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>37,3%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>45,39%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>40,06%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>42,92%</t>
-        </is>
-      </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
           <t>35,08%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,65; 45,05</t>
+          <t>34,32; 44,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>39,43; 50,56</t>
+          <t>39,73; 50,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28,1; 38,03</t>
+          <t>28,26; 38,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38,57; 48,0</t>
+          <t>37,96; 47,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,73; 46,52</t>
+          <t>35,62; 46,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,33; 46,7</t>
+          <t>35,5; 46,9</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,41; 42,92</t>
+          <t>32,15; 42,36</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>40,85; 49,46</t>
+          <t>41,64; 49,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36,51; 43,52</t>
+          <t>36,19; 43,43</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39,08; 46,98</t>
+          <t>39,1; 46,97</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>31,28; 38,46</t>
+          <t>31,45; 38,85</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>40,98; 47,44</t>
+          <t>40,91; 47,3</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>67,48%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>50,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>39,51; 47,61</t>
+          <t>39,77; 48,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>46,02; 54,35</t>
+          <t>45,57; 53,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39,3; 48,14</t>
+          <t>39,44; 48,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>47,11; 87,53</t>
+          <t>42,56; 52,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>48,07; 64,12</t>
+          <t>48,71; 64,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,41; 61,85</t>
+          <t>49,81; 61,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>40,34; 55,97</t>
+          <t>39,24; 55,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>52,13; 64,08</t>
+          <t>50,97; 63,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42,99; 50,38</t>
+          <t>43,02; 50,43</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>48,07; 54,92</t>
+          <t>48,42; 55,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40,8; 48,29</t>
+          <t>40,66; 48,47</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50,41; 84,92</t>
+          <t>46,56; 54,12</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>49,59%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>45,25; 50,88</t>
+          <t>44,84; 50,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>44,08; 50,44</t>
+          <t>44,23; 50,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>40,37; 46,33</t>
+          <t>40,64; 46,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,01; 51,7</t>
+          <t>44,67; 50,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>50,35; 57,97</t>
+          <t>50,29; 57,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,25; 51,44</t>
+          <t>44,17; 51,63</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,74; 47,89</t>
+          <t>40,69; 47,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,43; 80,28</t>
+          <t>48,74; 54,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>47,99; 52,54</t>
+          <t>47,79; 52,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45,25; 50,05</t>
+          <t>45,32; 50,03</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41,42; 45,82</t>
+          <t>41,59; 46,19</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>49,35; 70,62</t>
+          <t>47,35; 51,92</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53,48%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>57,16%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>44,1; 55,07</t>
+          <t>43,95; 55,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>42,67; 51,04</t>
+          <t>42,1; 50,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,06; 46,17</t>
+          <t>37,95; 45,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>48,34; 58,0</t>
+          <t>47,18; 56,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>54,67; 62,82</t>
+          <t>54,21; 62,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,76; 65,73</t>
+          <t>58,35; 65,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,4; 58,82</t>
+          <t>51,35; 58,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>41,64; 62,97</t>
+          <t>57,86; 63,5</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>51,59; 58,2</t>
+          <t>51,79; 58,45</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>53,07; 58,86</t>
+          <t>53,2; 58,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>46,36; 51,83</t>
+          <t>46,31; 51,71</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>43,71; 58,99</t>
+          <t>54,6; 59,76</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>55,41%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,59%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>13,69; 22,62</t>
+          <t>13,36; 22,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>18,72; 29,52</t>
+          <t>18,44; 29,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>16,59; 26,52</t>
+          <t>16,43; 26,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13,69; 30,53</t>
+          <t>13,5; 29,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>62,44; 67,67</t>
+          <t>62,76; 67,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56,82; 62,79</t>
+          <t>56,93; 63,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,73; 57,04</t>
+          <t>50,53; 56,64</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>53,05; 60,22</t>
+          <t>51,96; 58,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>53,64; 58,52</t>
+          <t>53,32; 58,28</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50,54; 55,6</t>
+          <t>50,17; 55,59</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44,2; 49,7</t>
+          <t>44,12; 49,65</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>44,56; 51,7</t>
+          <t>44,12; 50,74</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>52,46%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>40,77; 44,25</t>
+          <t>40,74; 44,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42,3; 45,79</t>
+          <t>42,18; 45,71</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37,36; 40,63</t>
+          <t>37,17; 40,53</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>45,29; 62,36</t>
+          <t>43,61; 47,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>55,28; 58,7</t>
+          <t>55,15; 58,69</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,39; 55,89</t>
+          <t>52,61; 55,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>46,01; 49,53</t>
+          <t>46,1; 49,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>51,03; 63,37</t>
+          <t>51,61; 54,67</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>48,69; 51,1</t>
+          <t>48,59; 51,11</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>47,95; 50,46</t>
+          <t>48,05; 50,58</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>42,28; 44,68</t>
+          <t>42,21; 44,67</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,23; 59,16</t>
+          <t>48,27; 50,57</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>231058</t>
+          <t>251125</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>192759</t>
+          <t>210504</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>423817</t>
+          <t>461629</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>171982; 214669</t>
+          <t>170616; 212360</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>136804; 179861</t>
+          <t>138598; 181123</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>129566; 168502</t>
+          <t>129946; 169634</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>206855; 253541</t>
+          <t>228142; 276016</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>131320; 165400</t>
+          <t>130400; 166479</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>116468; 153109</t>
+          <t>114762; 153358</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97716; 132875</t>
+          <t>99062; 134431</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>175836; 210377</t>
+          <t>193785; 228999</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313385; 367317</t>
+          <t>313146; 367429</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>266538; 320558</t>
+          <t>264186; 320008</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>236710; 291077</t>
+          <t>239202; 292909</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>395063; 451719</t>
+          <t>432172; 494670</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>193778</t>
+          <t>204876</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>173400</t>
+          <t>193490</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>367177</t>
+          <t>398366</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>127160; 165312</t>
+          <t>125946; 163450</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>165124; 211740</t>
+          <t>166385; 211535</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>105999; 143478</t>
+          <t>106610; 144934</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>174119; 216709</t>
+          <t>183052; 229263</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>132870; 172977</t>
+          <t>132474; 171626</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>119435; 157867</t>
+          <t>120000; 158529</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>120656; 159780</t>
+          <t>119693; 157703</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>156032; 188957</t>
+          <t>175937; 209861</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>269715; 321556</t>
+          <t>267359; 320896</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>295729; 355579</t>
+          <t>295946; 355439</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>234474; 288248</t>
+          <t>235699; 291190</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>341536; 395373</t>
+          <t>370119; 427891</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>448995</t>
+          <t>221607</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>96412</t>
+          <t>106766</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>545408</t>
+          <t>328374</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>214276; 258246</t>
+          <t>215704; 260857</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>289643; 342099</t>
+          <t>286826; 339784</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>205117; 251260</t>
+          <t>205819; 252372</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>313458; 582420</t>
+          <t>199472; 244632</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>80659; 107577</t>
+          <t>81724; 107579</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>128524; 160877</t>
+          <t>129570; 161236</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>67020; 92979</t>
+          <t>65183; 92265</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>86492; 106330</t>
+          <t>95026; 118081</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>305282; 357787</t>
+          <t>305539; 358104</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>427605; 488505</t>
+          <t>430718; 494820</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>280689; 332277</t>
+          <t>279737; 333481</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>419056; 705891</t>
+          <t>305044; 354548</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>498428</t>
+          <t>538307</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>607664</t>
+          <t>446075</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1106093</t>
+          <t>984382</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>560304; 630059</t>
+          <t>555295; 623755</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>510854; 584660</t>
+          <t>512686; 581963</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>464139; 532680</t>
+          <t>467194; 533010</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>463519; 532415</t>
+          <t>503070; 571554</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>359646; 414093</t>
+          <t>359208; 412251</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>339233; 394345</t>
+          <t>338633; 395833</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>336495; 395549</t>
+          <t>336052; 393797</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>501873; 783371</t>
+          <t>418606; 472157</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>937149; 1025809</t>
+          <t>933116; 1025549</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>871347; 963809</t>
+          <t>872729; 963338</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>818216; 905166</t>
+          <t>821589; 912509</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>989790; 1416338</t>
+          <t>939944; 1030648</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>251572</t>
+          <t>291470</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>459500</t>
+          <t>502371</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>711071</t>
+          <t>793841</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>154591; 193034</t>
+          <t>154083; 193368</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>217860; 260603</t>
+          <t>214963; 260226</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>236258; 286575</t>
+          <t>235569; 283507</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>227433; 272873</t>
+          <t>265585; 319746</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>310945; 357316</t>
+          <t>308322; 356554</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>447438; 500570</t>
+          <t>444332; 500271</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>379425; 434241</t>
+          <t>379055; 433074</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>348371; 526828</t>
+          <t>477877; 524518</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>474256; 535028</t>
+          <t>476126; 537362</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>675073; 748814</t>
+          <t>676713; 746823</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>630032; 704354</t>
+          <t>629329; 702718</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>571351; 771029</t>
+          <t>758399; 830071</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>50381</t>
+          <t>47600</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>426451</t>
+          <t>462794</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>476832</t>
+          <t>510395</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40811; 67453</t>
+          <t>39842; 66672</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>49959; 78787</t>
+          <t>49208; 77650</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>47628; 76151</t>
+          <t>47173; 76249</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32925; 73425</t>
+          <t>32031; 69770</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>779739; 845004</t>
+          <t>783703; 845671</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>630292; 696580</t>
+          <t>631571; 700309</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>548892; 617164</t>
+          <t>546760; 612900</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>399301; 453217</t>
+          <t>433953; 492702</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>829746; 905247</t>
+          <t>824904; 901545</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>695603; 765175</t>
+          <t>690455; 765056</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>605234; 680483</t>
+          <t>604030; 679764</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>442574; 513487</t>
+          <t>473194; 544163</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1674213</t>
+          <t>1554986</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>1956186</t>
+          <t>1922000</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3630398</t>
+          <t>3476987</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1333166; 1446918</t>
+          <t>1332327; 1447040</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1447413; 1566864</t>
+          <t>1443301; 1564246</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1264804; 1375769</t>
+          <t>1258379; 1372338</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1521905; 2095734</t>
+          <t>1493745; 1619516</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1867456; 1983039</t>
+          <t>1863067; 1982543</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1859988; 1984006</t>
+          <t>1867881; 1982584</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1624911; 1749141</t>
+          <t>1628062; 1747588</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>1816313; 2255467</t>
+          <t>1866231; 1976780</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3236790; 3397505</t>
+          <t>3230199; 3398267</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3343100; 3518116</t>
+          <t>3350054; 3526349</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>2924978; 3090987</t>
+          <t>2919574; 3090131</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3406847; 4093778</t>
+          <t>3398979; 3560890</t>
         </is>
       </c>
     </row>
